--- a/consultation-dashboard/test-data/sample1_normal.xlsx
+++ b/consultation-dashboard/test-data/sample1_normal.xlsx
@@ -417,13 +417,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -447,6 +448,11 @@
           <t>담당자</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>상담유형</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -467,6 +473,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -487,6 +498,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -507,6 +523,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -527,6 +548,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -547,6 +573,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -567,6 +598,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -587,6 +623,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -607,6 +648,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -627,6 +673,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -647,6 +698,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -667,6 +723,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>재진</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -687,6 +748,11 @@
           <t>박상담</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -707,6 +773,11 @@
           <t>김상담</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>초진</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -725,6 +796,11 @@
       <c r="D15" t="inlineStr">
         <is>
           <t>김상담</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>재진</t>
         </is>
       </c>
     </row>
